--- a/extracao.xlsx
+++ b/extracao.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Decision_Trees.pdf</t>
+          <t>papers/Decision_Trees.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/DeepLearning initialization review.pdf</t>
+          <t>papers/DeepLearning initialization review.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/HyperNeat.pdf</t>
+          <t>papers/HyperNeat.pdf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/hyperneat_application.pdf</t>
+          <t>papers/hyperneat_application.pdf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -525,7 +525,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Image self supervision.pdf</t>
+          <t>papers/Image self supervision.pdf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Intoduction to Statistical Learning.pdf</t>
+          <t>papers/Intoduction to Statistical Learning.pdf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/ISITC2016_paper_30.pdf</t>
+          <t>papers/ISITC2016_paper_30.pdf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Neat Roving Eye.pdf</t>
+          <t>papers/Neat Roving Eye.pdf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -597,7 +597,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Neat x Hyperneat - strategic decisions.pdf</t>
+          <t>papers/Neat x Hyperneat - strategic decisions.pdf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -615,7 +615,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Neat.pdf</t>
+          <t>papers/Neat.pdf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Neural machine translation by jointly learning to align and translate.pdf</t>
+          <t>papers/Neural machine translation by jointly learning to align and translate.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Novelty Search.pdf</t>
+          <t>papers/Novelty Search.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Probability and Statistics notes.pdf</t>
+          <t>papers/Probability and Statistics notes.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Reward-is-enough_2021_Artificial-Intelligence.pdf</t>
+          <t>papers/Reward-is-enough_2021_Artificial-Intelligence.pdf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/robust_regression.pdf</t>
+          <t>papers/robust_regression.pdf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Robust_Regression_comparision.pdf</t>
+          <t>papers/Robust_Regression_comparision.pdf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/RTNeat.pdf</t>
+          <t>papers/RTNeat.pdf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -763,7 +763,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/statquest_t_sne_and_umap_study_guide_v1.pdf</t>
+          <t>papers/statquest_t_sne_and_umap_study_guide_v1.pdf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/SuttonBartoIPRLBook2ndEd.pdf</t>
+          <t>papers/SuttonBartoIPRLBook2ndEd.pdf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/what_matters_for_on_policy_dee.pdf</t>
+          <t>papers/what_matters_for_on_policy_dee.pdf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/2011 The kaldi speech recognition_toolkit.pdf</t>
+          <t>papers/Audio/2011 The kaldi speech recognition_toolkit.pdf</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/2023 Seamless.pdf</t>
+          <t>papers/Audio/2023 Seamless.pdf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/2023 SeamlessM4T.pdf</t>
+          <t>papers/Audio/2023 SeamlessM4T.pdf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -875,7 +875,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/2023 SpeechX.pdf</t>
+          <t>papers/Audio/2023 SpeechX.pdf</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -897,7 +897,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/2023 Voicebox(1).pdf</t>
+          <t>papers/Audio/2023 Voicebox(1).pdf</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/2023 VoiceBox.pdf</t>
+          <t>papers/Audio/2023 VoiceBox.pdf</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -933,7 +933,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/2024 MASKED AUDIO GENERATION USING A SINGLE NON-_AUTOREGRESSIVE TRANSFORMER.pdf</t>
+          <t>papers/Audio/2024 MASKED AUDIO GENERATION USING A SINGLE NON-_AUTOREGRESSIVE TRANSFORMER.pdf</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/2024 Parallel Fast Pitch.pdf</t>
+          <t>papers/Audio/2024 Parallel Fast Pitch.pdf</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -977,7 +977,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/2024 SpeechVerse.pdf</t>
+          <t>papers/Audio/2024 SpeechVerse.pdf</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Attention-Based Models for Speech Recognition.pdf</t>
+          <t>papers/Audio/Attention-Based Models for Speech Recognition.pdf</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Audio representations for deep learning in sound_synthesis_ A review.pdf</t>
+          <t>papers/Audio/Audio representations for deep learning in sound_synthesis_ A review.pdf</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1043,7 +1043,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/AudioLM.pdf</t>
+          <t>papers/Audio/AudioLM.pdf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Automatic Speech Recognition_ A Deep Learning_Approach.pdf</t>
+          <t>papers/Audio/Automatic Speech Recognition_ A Deep Learning_Approach.pdf</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/MelNet_ A Generative Model for Audio in the Frequency Domain.pdf</t>
+          <t>papers/Audio/MelNet_ A Generative Model for Audio in the Frequency Domain.pdf</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1105,7 +1105,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/MFA_paper_Interspeech2017.pdf</t>
+          <t>papers/Audio/MFA_paper_Interspeech2017.pdf</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/SoundStream.pdf</t>
+          <t>papers/Audio/SoundStream.pdf</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1145,7 +1145,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Theory and Applications of Digital Speech_Processing.pdf</t>
+          <t>papers/Audio/Theory and Applications of Digital Speech_Processing.pdf</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/VALL-E.pdf</t>
+          <t>papers/Audio/VALL-E.pdf</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1185,7 +1185,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Voicebox.pdf</t>
+          <t>papers/Audio/Voicebox.pdf</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1203,7 +1203,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/WaveGlow.pdf</t>
+          <t>papers/Audio/WaveGlow.pdf</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1225,7 +1225,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/whisper.pdf</t>
+          <t>papers/Audio/whisper.pdf</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1243,7 +1243,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Boosting/XGBoost.pdf</t>
+          <t>papers/Boosting/XGBoost.pdf</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1265,7 +1265,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Clustering/FUZZY C MEANS.pdf</t>
+          <t>papers/Clustering/FUZZY C MEANS.pdf</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Deep Learning/2024 Kolmogorov–Arnold Networks.pdf</t>
+          <t>papers/Deep Learning/2024 Kolmogorov–Arnold Networks.pdf</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1305,7 +1305,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Deep Learning/Gumbel Softmax.pdf</t>
+          <t>papers/Deep Learning/Gumbel Softmax.pdf</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1327,7 +1327,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/2022 Scalable Diffusion Models with Transformers.pdf</t>
+          <t>papers/Diffusion Models/2022 Scalable Diffusion Models with Transformers.pdf</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1349,7 +1349,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/2023 DIFFUSION-GAN.pdf</t>
+          <t>papers/Diffusion Models/2023 DIFFUSION-GAN.pdf</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/2024 LiteVAE.pdf</t>
+          <t>papers/Diffusion Models/2024 LiteVAE.pdf</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/2024 META Emu.pdf</t>
+          <t>papers/Diffusion Models/2024 META Emu.pdf</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/2024 META Imagine Flash.pdf</t>
+          <t>papers/Diffusion Models/2024 META Imagine Flash.pdf</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1433,7 +1433,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/2024 Multistep Consistency Models.pdf</t>
+          <t>papers/Diffusion Models/2024 Multistep Consistency Models.pdf</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/2024 PIXART-δ.pdf</t>
+          <t>papers/Diffusion Models/2024 PIXART-δ.pdf</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1477,7 +1477,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/2024 PixArt-Σ.pdf</t>
+          <t>papers/Diffusion Models/2024 PixArt-Σ.pdf</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/2024 Scalable High-Resolution Pixel-Space Image Synthesis with_Hourglass Diffusion Transformers.pdf</t>
+          <t>papers/Diffusion Models/2024 Scalable High-Resolution Pixel-Space Image Synthesis with_Hourglass Diffusion Transformers.pdf</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/2024 Self-Cascade Diffusion Model_for Higher-Resolution Adaptation.pdf</t>
+          <t>papers/Diffusion Models/2024 Self-Cascade Diffusion Model_for Higher-Resolution Adaptation.pdf</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1543,7 +1543,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/2024 Stable Diffusion 3.pdf</t>
+          <t>papers/Diffusion Models/2024 Stable Diffusion 3.pdf</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1565,7 +1565,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/2024 Zero-shot Identity-Preserving_Generation in Seconds.pdf</t>
+          <t>papers/Diffusion Models/2024 Zero-shot Identity-Preserving_Generation in Seconds.pdf</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/Cascaded diffusion models for high fidelity image generation.pdf</t>
+          <t>papers/Diffusion Models/Cascaded diffusion models for high fidelity image generation.pdf</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/Classifier-free diffusion guidance.pdf</t>
+          <t>papers/Diffusion Models/Classifier-free diffusion guidance.pdf</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/DALL-E.pdf</t>
+          <t>papers/Diffusion Models/DALL-E.pdf</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/DENOISING DIFFUSION IMPLICIT MODELS.pdf</t>
+          <t>papers/Diffusion Models/DENOISING DIFFUSION IMPLICIT MODELS.pdf</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1675,7 +1675,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/denoising diffusion probabilistic models.pdf</t>
+          <t>papers/Diffusion Models/denoising diffusion probabilistic models.pdf</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1697,7 +1697,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/diffusion models beat gans.pdf</t>
+          <t>papers/Diffusion Models/diffusion models beat gans.pdf</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1719,7 +1719,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/GLIDE.pdf</t>
+          <t>papers/Diffusion Models/GLIDE.pdf</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/Imagen.pdf</t>
+          <t>papers/Diffusion Models/Imagen.pdf</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1763,7 +1763,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/ImagenVideo.pdf</t>
+          <t>papers/Diffusion Models/ImagenVideo.pdf</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/Imagic.pdf</t>
+          <t>papers/Diffusion Models/Imagic.pdf</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/Improved Denoising Diffusion Probabilistic Models.pdf</t>
+          <t>papers/Diffusion Models/Improved Denoising Diffusion Probabilistic Models.pdf</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1825,7 +1825,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/PixelCNN++.pdf</t>
+          <t>papers/Diffusion Models/PixelCNN++.pdf</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/RePaint.pdf</t>
+          <t>papers/Diffusion Models/RePaint.pdf</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1865,7 +1865,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/RePaint_ Inpainting using Denoising Diffusion Probabilistic Models.pdf</t>
+          <t>papers/Diffusion Models/RePaint_ Inpainting using Denoising Diffusion Probabilistic Models.pdf</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/Resolution-robust large mask inpainting with_fourier convolutions.pdf</t>
+          <t>papers/Diffusion Models/Resolution-robust large mask inpainting with_fourier convolutions.pdf</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1905,7 +1905,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/SDEdit.pdf</t>
+          <t>papers/Diffusion Models/SDEdit.pdf</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1927,7 +1927,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/SRDiff.pdf</t>
+          <t>papers/Diffusion Models/SRDiff.pdf</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/StableDiffusion.pdf</t>
+          <t>papers/Diffusion Models/StableDiffusion.pdf</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1971,7 +1971,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/VQGAN.pdf</t>
+          <t>papers/Diffusion Models/VQGAN.pdf</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Efficient/202403 GaLore.pdf</t>
+          <t>papers/Efficient/202403 GaLore.pdf</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2015,7 +2015,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Efficient/202407 Q-GaLore.pdf</t>
+          <t>papers/Efficient/202407 Q-GaLore.pdf</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2037,7 +2037,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/GAN/Projected GAN.pdf</t>
+          <t>papers/GAN/Projected GAN.pdf</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/GAN/State-of-the-Art in the Architecture, Methods and Applications of_StyleGAN.pdf</t>
+          <t>papers/GAN/State-of-the-Art in the Architecture, Methods and Applications of_StyleGAN.pdf</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2081,7 +2081,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/GAN/StyleGAN T.pdf</t>
+          <t>papers/GAN/StyleGAN T.pdf</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/GAN/styleGAN.pdf</t>
+          <t>papers/GAN/styleGAN.pdf</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2125,7 +2125,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/GAN/StyleGAN_2.pdf</t>
+          <t>papers/GAN/StyleGAN_2.pdf</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/GAN/StyleGAN_2_ADA.pdf</t>
+          <t>papers/GAN/StyleGAN_2_ADA.pdf</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/2020 DeepFaceSwap.pdf</t>
+          <t>papers/Generative/2020 DeepFaceSwap.pdf</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2191,7 +2191,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/2023 gigaGAN.pdf</t>
+          <t>papers/Generative/2023 gigaGAN.pdf</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2209,7 +2209,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/Consistency models.pdf</t>
+          <t>papers/Generative/Consistency models.pdf</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2231,7 +2231,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/Fader Networks_Manipulating Images by Sliding Attributes.pdf</t>
+          <t>papers/Generative/Fader Networks_Manipulating Images by Sliding Attributes.pdf</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/Generating Diverse High-Fidelity Images_with VQ-VAE-2.pdf</t>
+          <t>papers/Generative/Generating Diverse High-Fidelity Images_with VQ-VAE-2.pdf</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/Latent Space Factorisation and Manipulation via Matrix Subspace Projection.pdf</t>
+          <t>papers/Generative/Latent Space Factorisation and Manipulation via Matrix Subspace Projection.pdf</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/Learning Latent Subspaces in_Variational Autoencoder.pdf</t>
+          <t>papers/Generative/Learning Latent Subspaces in_Variational Autoencoder.pdf</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2315,7 +2315,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/Lydia_Reverse_Variational_Autoencoder_for_Visual_Attribute_Manipulation_and_Anomaly_Detection_WACV_2020_paper.pdf</t>
+          <t>papers/Generative/Lydia_Reverse_Variational_Autoencoder_for_Visual_Attribute_Manipulation_and_Anomaly_Detection_WACV_2020_paper.pdf</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2333,7 +2333,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/PARTI.pdf</t>
+          <t>papers/Generative/PARTI.pdf</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2355,7 +2355,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/Towards Robust Blind Face Restoration with_Codebook Lookup Transformer.pdf</t>
+          <t>papers/Generative/Towards Robust Blind Face Restoration with_Codebook Lookup Transformer.pdf</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2377,7 +2377,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Hyperparameters/2022 µP.pdf</t>
+          <t>papers/Hyperparameters/2022 µP.pdf</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Image/2024 VISION TRANSFORMERS NEED REGISTERS.pdf</t>
+          <t>papers/Image/2024 VISION TRANSFORMERS NEED REGISTERS.pdf</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2421,7 +2421,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Image/Vision Transformer.pdf</t>
+          <t>papers/Image/Vision Transformer.pdf</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2443,7 +2443,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/2023 A Survey on Multimodal Large Language Models.pdf</t>
+          <t>papers/Multimodal/2023 A Survey on Multimodal Large Language Models.pdf</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2465,7 +2465,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/2023 Cheap and Quick Efficient Vision-Language_Instruction Tuning for Large Language Models.pdf</t>
+          <t>papers/Multimodal/2023 Cheap and Quick Efficient Vision-Language_Instruction Tuning for Large Language Models.pdf</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/2023 How to Bridge the Gap between Modalities_ A_Comprehensive Survey on Multi-modal Large_Language Model.pdf</t>
+          <t>papers/Multimodal/2023 How to Bridge the Gap between Modalities_ A_Comprehensive Survey on Multi-modal Large_Language Model.pdf</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2509,7 +2509,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/2023 LLAVA.pdf</t>
+          <t>papers/Multimodal/2023 LLAVA.pdf</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2531,7 +2531,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/2023 NExT-GPT_ Any-to-Any Multimodal LLM.pdf</t>
+          <t>papers/Multimodal/2023 NExT-GPT_ Any-to-Any Multimodal LLM.pdf</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2553,7 +2553,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/2023 Versatile Vision Encoders for Multimodal Large Language Models.pdf</t>
+          <t>papers/Multimodal/2023 Versatile Vision Encoders for Multimodal Large Language Models.pdf</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/2024 An Automated Pipeline for Generating Synthetic_Multi-modal Datasets.pdf</t>
+          <t>papers/Multimodal/2024 An Automated Pipeline for Generating Synthetic_Multi-modal Datasets.pdf</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2597,7 +2597,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/2024 Byte Models are Digital World Simulators.pdf</t>
+          <t>papers/Multimodal/2024 Byte Models are Digital World Simulators.pdf</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2619,7 +2619,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/2024 Recent Advances in MultiModal Large Language Models.pdf</t>
+          <t>papers/Multimodal/2024 Recent Advances in MultiModal Large Language Models.pdf</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2641,7 +2641,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/20240518 Uni-MoE.pdf</t>
+          <t>papers/Multimodal/20240518 Uni-MoE.pdf</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/202408 LAW OF VISION REPRESENTATION IN MLLMS.pdf</t>
+          <t>papers/Multimodal/202408 LAW OF VISION REPRESENTATION IN MLLMS.pdf</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2685,7 +2685,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/improved_llava.pdf</t>
+          <t>papers/Multimodal/improved_llava.pdf</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2703,7 +2703,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/2017 Efficient Natural Language Response Suggestion_for Smart Reply.pdf</t>
+          <t>papers/NLP/2017 Efficient Natural Language Response Suggestion_for Smart Reply.pdf</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2725,7 +2725,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/2019 A CONDITIONAL TRANSFORMER LANGUAGE_MODEL FOR CONTROLLABLE GENERATION.pdf</t>
+          <t>papers/NLP/2019 A CONDITIONAL TRANSFORMER LANGUAGE_MODEL FOR CONTROLLABLE GENERATION.pdf</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2747,7 +2747,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/2020 The curious case of neural_text degeneration.pdf</t>
+          <t>papers/NLP/2020 The curious case of neural_text degeneration.pdf</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2769,7 +2769,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/2021 Prefix Tunning.pdf</t>
+          <t>papers/NLP/2021 Prefix Tunning.pdf</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/2022 A contrastive frame-_work for neural text generation.pdf</t>
+          <t>papers/NLP/2022 A contrastive frame-_work for neural text generation.pdf</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2813,7 +2813,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/2022 Foundation Transformer.pdf</t>
+          <t>papers/NLP/2022 Foundation Transformer.pdf</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2835,7 +2835,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/2023 Contrastive Search Is What You Need For_Neural Text Generation.pdf</t>
+          <t>papers/NLP/2023 Contrastive Search Is What You Need For_Neural Text Generation.pdf</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2857,7 +2857,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/2024 Evolutionary Optimization of Model Merging Recipes.pdf</t>
+          <t>papers/NLP/2024 Evolutionary Optimization of Model Merging Recipes.pdf</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2879,7 +2879,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Attention_is_all_you_need.pdf</t>
+          <t>papers/NLP/Attention_is_all_you_need.pdf</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2901,7 +2901,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/How to fine tune BERT for text classification.pdf</t>
+          <t>papers/NLP/How to fine tune BERT for text classification.pdf</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2923,7 +2923,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Quantization/2024 OneBit.pdf</t>
+          <t>papers/Quantization/2024 OneBit.pdf</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2945,7 +2945,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Reinforcement/2024 Grandmaster-Level Chess Without Search.pdf</t>
+          <t>papers/Reinforcement/2024 Grandmaster-Level Chess Without Search.pdf</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2967,7 +2967,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Reinforcement/2024 Learning H-Infinity Locomotion Control.pdf</t>
+          <t>papers/Reinforcement/2024 Learning H-Infinity Locomotion Control.pdf</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2989,7 +2989,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Reinforcement/2024 Training Value Functions via_Classification for Scalable Deep RL.pdf</t>
+          <t>papers/Reinforcement/2024 Training Value Functions via_Classification for Scalable Deep RL.pdf</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3011,7 +3011,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Reinforcement/Double Q Learning.pdf</t>
+          <t>papers/Reinforcement/Double Q Learning.pdf</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3033,7 +3033,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Reinforcement/Dream v2.pdf</t>
+          <t>papers/Reinforcement/Dream v2.pdf</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3055,7 +3055,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Reinforcement/Dreams v1.pdf</t>
+          <t>papers/Reinforcement/Dreams v1.pdf</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3077,7 +3077,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Reinforcement/PPG.pdf</t>
+          <t>papers/Reinforcement/PPG.pdf</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/SelfSupervised/2023 A Cookbook of Self-Supervised Learning.pdf</t>
+          <t>papers/SelfSupervised/2023 A Cookbook of Self-Supervised Learning.pdf</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/SelfSupervised/A Simple Framework for Contrastive Learning of Visual Representations.pdf</t>
+          <t>papers/SelfSupervised/A Simple Framework for Contrastive Learning of Visual Representations.pdf</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3143,7 +3143,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/SelfSupervised/Barlow Twins_ Self-Supervised Learning via Redundancy Reduction.pdf</t>
+          <t>papers/SelfSupervised/Barlow Twins_ Self-Supervised Learning via Redundancy Reduction.pdf</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3165,7 +3165,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/SelfSupervised/Bootstrap Your Own Latent_A New Approach to Self-Supervised Learning.pdf</t>
+          <t>papers/SelfSupervised/Bootstrap Your Own Latent_A New Approach to Self-Supervised Learning.pdf</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3187,7 +3187,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/SelfSupervised/Deep Clustering for Unsupervised Learning_of Visual Features.pdf</t>
+          <t>papers/SelfSupervised/Deep Clustering for Unsupervised Learning_of Visual Features.pdf</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3209,7 +3209,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/SelfSupervised/Efficient Self-supervised Learning with Contextualized Target Representations_for Vision, Speech and Language.pdf</t>
+          <t>papers/SelfSupervised/Efficient Self-supervised Learning with Contextualized Target Representations_for Vision, Speech and Language.pdf</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3227,7 +3227,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/SelfSupervised/LARS.pdf</t>
+          <t>papers/SelfSupervised/LARS.pdf</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3249,7 +3249,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/SelfSupervised/Masked Autoencoders Are Scalable Vision Learners.pdf</t>
+          <t>papers/SelfSupervised/Masked Autoencoders Are Scalable Vision Learners.pdf</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3271,7 +3271,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/SelfSupervised/Unsupervised Learning of Visual Features_by Contrasting Cluster Assignments.pdf</t>
+          <t>papers/SelfSupervised/Unsupervised Learning of Visual Features_by Contrasting Cluster Assignments.pdf</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/SelfSupervised/VicReg.pdf</t>
+          <t>papers/SelfSupervised/VicReg.pdf</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3315,7 +3315,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/State space/2022 Efficient Long Sequence Modeling via State Space Augmented_Transformer.pdf</t>
+          <t>papers/State space/2022 Efficient Long Sequence Modeling via State Space Augmented_Transformer.pdf</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3337,7 +3337,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/State space/2022 S4.pdf</t>
+          <t>papers/State space/2022 S4.pdf</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3359,7 +3359,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/State space/2023 Hungry Hungry Hippos.pdf</t>
+          <t>papers/State space/2023 Hungry Hungry Hippos.pdf</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3381,7 +3381,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/State space/2023 Hyena Hierarchy.pdf</t>
+          <t>papers/State space/2023 Hyena Hierarchy.pdf</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/State space/2023 Mamba.pdf</t>
+          <t>papers/State space/2023 Mamba.pdf</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/State space/2023 Retention Network.pdf</t>
+          <t>papers/State space/2023 Retention Network.pdf</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/State space/2024 BlackMamba.pdf</t>
+          <t>papers/State space/2024 BlackMamba.pdf</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/State space/2024 JAMBA.pdf</t>
+          <t>papers/State space/2024 JAMBA.pdf</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3487,7 +3487,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/State space/2024 Moe Mamba.pdf</t>
+          <t>papers/State space/2024 Moe Mamba.pdf</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3509,7 +3509,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/State space/202406 SAMBA.pdf</t>
+          <t>papers/State space/202406 SAMBA.pdf</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3531,7 +3531,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Embeddings/2020 wav2vec 2.0.pdf</t>
+          <t>papers/Audio/Embeddings/2020 wav2vec 2.0.pdf</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3553,7 +3553,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Embeddings/2021 Conformer.pdf</t>
+          <t>papers/Audio/Embeddings/2021 Conformer.pdf</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3575,7 +3575,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Embeddings/2021 HuBert.pdf</t>
+          <t>papers/Audio/Embeddings/2021 HuBert.pdf</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3597,7 +3597,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Embeddings/2021 W2V-BERT.pdf</t>
+          <t>papers/Audio/Embeddings/2021 W2V-BERT.pdf</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3619,7 +3619,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Embeddings/2022 EnCodec - High Fidelity Neural Audio Compression.pdf</t>
+          <t>papers/Audio/Embeddings/2022 EnCodec - High Fidelity Neural Audio Compression.pdf</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3641,7 +3641,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Embeddings/2024 ZipFormer.pdf</t>
+          <t>papers/Audio/Embeddings/2024 ZipFormer.pdf</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3663,7 +3663,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Embeddings/WaveNet.pdf</t>
+          <t>papers/Audio/Embeddings/WaveNet.pdf</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Encoding/202408 WAVTOKENIZER.pdf</t>
+          <t>papers/Audio/Encoding/202408 WAVTOKENIZER.pdf</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3707,7 +3707,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/LLM/Towards Achieving Human Parity on End-to-end_Simultaneous Speech Translation.pdf</t>
+          <t>papers/Audio/LLM/Towards Achieving Human Parity on End-to-end_Simultaneous Speech Translation.pdf</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3729,7 +3729,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Translation/2019 Translatotoron 1.pdf</t>
+          <t>papers/Audio/Translation/2019 Translatotoron 1.pdf</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3751,7 +3751,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Translation/Translatotron 2.pdf</t>
+          <t>papers/Audio/Translation/Translatotron 2.pdf</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3773,7 +3773,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Translation/Translatotron 3.pdf</t>
+          <t>papers/Audio/Translation/Translatotron 3.pdf</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3795,7 +3795,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/2017 Tacotron.pdf</t>
+          <t>papers/Audio/TTS/2017 Tacotron.pdf</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3817,7 +3817,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/2018 Tacotron 2.pdf</t>
+          <t>papers/Audio/TTS/2018 Tacotron 2.pdf</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3839,7 +3839,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/2019 FastSpeech.pdf</t>
+          <t>papers/Audio/TTS/2019 FastSpeech.pdf</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/2019 GAN-TTS.pdf</t>
+          <t>papers/Audio/TTS/2019 GAN-TTS.pdf</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/2019 Neural Speech Synthesis with Transformer Network(1).pdf</t>
+          <t>papers/Audio/TTS/2019 Neural Speech Synthesis with Transformer Network(1).pdf</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3905,7 +3905,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/2019 Neural Speech Synthesis with Transformer Network.pdf</t>
+          <t>papers/Audio/TTS/2019 Neural Speech Synthesis with Transformer Network.pdf</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3927,7 +3927,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/2020 Hifi GAN.pdf</t>
+          <t>papers/Audio/TTS/2020 Hifi GAN.pdf</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3949,7 +3949,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/2021 END-TO-END ADVERSARIAL TEXT-TO-SPEECH.pdf</t>
+          <t>papers/Audio/TTS/2021 END-TO-END ADVERSARIAL TEXT-TO-SPEECH.pdf</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3971,7 +3971,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/2021 FastSpeech 2.pdf</t>
+          <t>papers/Audio/TTS/2021 FastSpeech 2.pdf</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3993,7 +3993,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/2023 E3 TTS.pdf</t>
+          <t>papers/Audio/TTS/2023 E3 TTS.pdf</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4015,7 +4015,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/202305 NaturalSpeech 2.pdf</t>
+          <t>papers/Audio/TTS/202305 NaturalSpeech 2.pdf</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4037,7 +4037,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/2024 FlashSpeech.pdf</t>
+          <t>papers/Audio/TTS/2024 FlashSpeech.pdf</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4059,7 +4059,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/2024 NaturalSpeech 3.pdf</t>
+          <t>papers/Audio/TTS/2024 NaturalSpeech 3.pdf</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4081,7 +4081,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/TTS/EFFICIENTLY TRAINABLE TEXT-TO-SPEECH SYSTEM BASED ON_DEEP CONVOLUTIONAL NETWORKS .pdf</t>
+          <t>papers/Audio/TTS/EFFICIENTLY TRAINABLE TEXT-TO-SPEECH SYSTEM BASED ON_DEEP CONVOLUTIONAL NETWORKS .pdf</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4103,7 +4103,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Audio/Vocoder/2024 EVA-GAN.pdf</t>
+          <t>papers/Audio/Vocoder/2024 EVA-GAN.pdf</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4125,7 +4125,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Deep Learning/Attention/202409 Theory, Analysis, and Best Practices for_Sigmoid Self-Attention.pdf</t>
+          <t>papers/Deep Learning/Attention/202409 Theory, Analysis, and Best Practices for_Sigmoid Self-Attention.pdf</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4147,7 +4147,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Deep Learning/Optimizers/2017 Adam.pdf</t>
+          <t>papers/Deep Learning/Optimizers/2017 Adam.pdf</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4169,7 +4169,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Deep Learning/Optimizers/2019 AdamW.pdf</t>
+          <t>papers/Deep Learning/Optimizers/2019 AdamW.pdf</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4191,7 +4191,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Deep Learning/Optimizers/2023 Lion Optimizer.pdf</t>
+          <t>papers/Deep Learning/Optimizers/2023 Lion Optimizer.pdf</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4213,7 +4213,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Deep Learning/Optimizers/202409 THE ADEMAMIX OPTIMIZER.pdf</t>
+          <t>papers/Deep Learning/Optimizers/202409 THE ADEMAMIX OPTIMIZER.pdf</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4235,7 +4235,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/Models/202409 OmniGen.pdf</t>
+          <t>papers/Diffusion Models/Models/202409 OmniGen.pdf</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4257,7 +4257,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/Models/DALL-E 2.pdf</t>
+          <t>papers/Diffusion Models/Models/DALL-E 2.pdf</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4279,7 +4279,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Diffusion Models/SuperResolution/Super Resolution via iterative refinement.pdf</t>
+          <t>papers/Diffusion Models/SuperResolution/Super Resolution via iterative refinement.pdf</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/GAN/Models/alias-free GAN (stylegan3).pdf</t>
+          <t>papers/GAN/Models/alias-free GAN (stylegan3).pdf</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4323,7 +4323,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/GAN/Models/PROGAN.pdf</t>
+          <t>papers/GAN/Models/PROGAN.pdf</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4345,7 +4345,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/Autorregressive/20240610 Autoregressive Model Beats Diffusion.pdf</t>
+          <t>papers/Generative/Autorregressive/20240610 Autoregressive Model Beats Diffusion.pdf</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4367,7 +4367,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/VQ/2023 Make-A-Scene.pdf</t>
+          <t>papers/Generative/VQ/2023 Make-A-Scene.pdf</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4389,7 +4389,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/VQ/Autoregressive Image Generation using Residual Quantization.pdf</t>
+          <t>papers/Generative/VQ/Autoregressive Image Generation using Residual Quantization.pdf</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/VQ/DFVQGAN.pdf</t>
+          <t>papers/Generative/VQ/DFVQGAN.pdf</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4433,7 +4433,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/VQ/ViT VQGAN.pdf</t>
+          <t>papers/Generative/VQ/ViT VQGAN.pdf</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4455,7 +4455,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/VQ/VQGAN.pdf</t>
+          <t>papers/Generative/VQ/VQGAN.pdf</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4477,7 +4477,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Generative/VQ/VQVAE.pdf</t>
+          <t>papers/Generative/VQ/VQVAE.pdf</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4499,7 +4499,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Image/Autoencoder/Isolating Sources of Disentanglement in VAEs.pdf</t>
+          <t>papers/Image/Autoencoder/Isolating Sources of Disentanglement in VAEs.pdf</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4521,7 +4521,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Image/Classification/ResNet.pdf</t>
+          <t>papers/Image/Classification/ResNet.pdf</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4543,7 +4543,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Image/Metrics/The Unreasonable Effectiveness of Deep Features as a Perceptual Metric.pdf</t>
+          <t>papers/Image/Metrics/The Unreasonable Effectiveness of Deep Features as a Perceptual Metric.pdf</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4565,7 +4565,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/Embedding/CLIP.pdf</t>
+          <t>papers/Multimodal/Embedding/CLIP.pdf</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4587,7 +4587,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/ImageText/2023 PALI-3 VISION LANGUAGE MODELS.pdf</t>
+          <t>papers/Multimodal/ImageText/2023 PALI-3 VISION LANGUAGE MODELS.pdf</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4609,7 +4609,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/ImageText/2023 PALI-3.pdf</t>
+          <t>papers/Multimodal/ImageText/2023 PALI-3.pdf</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4631,7 +4631,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/ImageText/2023 Sigmoid Loss for Language Image Pre-Training.pdf</t>
+          <t>papers/Multimodal/ImageText/2023 Sigmoid Loss for Language Image Pre-Training.pdf</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4649,7 +4649,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/ImageText/2024 An Introduction to Vision-Language Modeling.pdf</t>
+          <t>papers/Multimodal/ImageText/2024 An Introduction to Vision-Language Modeling.pdf</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/ImageText/2024 Chameleon.pdf</t>
+          <t>papers/Multimodal/ImageText/2024 Chameleon.pdf</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4693,7 +4693,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Multimodal/ImageText/202406 Florence-2.pdf</t>
+          <t>papers/Multimodal/ImageText/202406 Florence-2.pdf</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4715,7 +4715,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Agents/2023 ReAct.pdf</t>
+          <t>papers/NLP/Agents/2023 ReAct.pdf</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4737,7 +4737,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Agents/2024 AutoWebGLM.pdf</t>
+          <t>papers/NLP/Agents/2024 AutoWebGLM.pdf</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4759,7 +4759,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Agents/2024 Executable Code Actions Elicit Better LLM Agents.pdf</t>
+          <t>papers/NLP/Agents/2024 Executable Code Actions Elicit Better LLM Agents.pdf</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4781,7 +4781,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Attention/2020 Fast autoregres-_sive transformers with linear attention.pdf</t>
+          <t>papers/NLP/Attention/2020 Fast autoregres-_sive transformers with linear attention.pdf</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4803,7 +4803,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Attention/2021 SELF-ATTENTION DOES NOT NEED O(n_2_) MEMORY.pdf</t>
+          <t>papers/NLP/Attention/2021 SELF-ATTENTION DOES NOT NEED O(n_2_) MEMORY.pdf</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4825,7 +4825,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Attention/2023 Blockwise Parallel Transformer_for Large Context Models.pdf</t>
+          <t>papers/NLP/Attention/2023 Blockwise Parallel Transformer_for Large Context Models.pdf</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4847,7 +4847,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Attention/2023 GQA_ Training Generalized Multi-Query Transformer Models from_Multi-Head Checkpoints.pdf</t>
+          <t>papers/NLP/Attention/2023 GQA_ Training Generalized Multi-Query Transformer Models from_Multi-Head Checkpoints.pdf</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4869,7 +4869,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Attention/2023 HyperAttention.pdf</t>
+          <t>papers/NLP/Attention/2023 HyperAttention.pdf</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4891,7 +4891,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Attention/2023 Ring Attention.pdf</t>
+          <t>papers/NLP/Attention/2023 Ring Attention.pdf</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4913,7 +4913,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Attention/2023 TransNormer.pdf</t>
+          <t>papers/NLP/Attention/2023 TransNormer.pdf</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4935,7 +4935,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Attention/2024 BurstAttention.pdf</t>
+          <t>papers/NLP/Attention/2024 BurstAttention.pdf</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4957,7 +4957,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Attention/2024 Lightning Attention-2.pdf</t>
+          <t>papers/NLP/Attention/2024 Lightning Attention-2.pdf</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4979,7 +4979,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Attention/Fast Autoregressive Transformers with Linear Attention.pdf</t>
+          <t>papers/NLP/Attention/Fast Autoregressive Transformers with Linear Attention.pdf</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5001,7 +5001,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Attention/Flash Attention.pdf</t>
+          <t>papers/NLP/Attention/Flash Attention.pdf</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5023,7 +5023,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Benchmarks/ARC.pdf</t>
+          <t>papers/NLP/Benchmarks/ARC.pdf</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5045,7 +5045,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Benchmarks/HellaSwag.pdf</t>
+          <t>papers/NLP/Benchmarks/HellaSwag.pdf</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5067,7 +5067,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Benchmarks/MMLU.pdf</t>
+          <t>papers/NLP/Benchmarks/MMLU.pdf</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Benchmarks/Truthfull QA.pdf</t>
+          <t>papers/NLP/Benchmarks/Truthfull QA.pdf</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5111,7 +5111,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Cache/2024 Layer-Condensed KV Cache.pdf</t>
+          <t>papers/NLP/Cache/2024 Layer-Condensed KV Cache.pdf</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5133,7 +5133,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Cache/LazyLLM_ DYNAMIC TOKEN PRUNING FOR EFFICIENT_LONG CONTEXT LLM INFERENCE.pdf</t>
+          <t>papers/NLP/Cache/LazyLLM_ DYNAMIC TOKEN PRUNING FOR EFFICIENT_LONG CONTEXT LLM INFERENCE.pdf</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Datasets/2022 The Pile.pdf</t>
+          <t>papers/NLP/Datasets/2022 The Pile.pdf</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5177,7 +5177,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Datasets/2023 EXPERTQA.pdf</t>
+          <t>papers/NLP/Datasets/2023 EXPERTQA.pdf</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5199,7 +5199,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Datasets/2023 Refined Web Dataset (FALCON).pdf</t>
+          <t>papers/NLP/Datasets/2023 Refined Web Dataset (FALCON).pdf</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Datasets/2023 The RefinedWeb Dataset for Falcon LLM.pdf</t>
+          <t>papers/NLP/Datasets/2023 The RefinedWeb Dataset for Falcon LLM.pdf</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5243,7 +5243,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Datasets/2024 How to Train Data-Efficient LLMs.pdf</t>
+          <t>papers/NLP/Datasets/2024 How to Train Data-Efficient LLMs.pdf</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5265,7 +5265,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Decoding/2024 Recurrent Drafter for Fast Speculative Decoding.pdf</t>
+          <t>papers/NLP/Decoding/2024 Recurrent Drafter for Fast Speculative Decoding.pdf</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5287,7 +5287,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Deploy/vLLM.pdf</t>
+          <t>papers/NLP/Deploy/vLLM.pdf</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5309,7 +5309,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2017 Efficient Natural Language Response Suggestion_for Smart Reply.pdf</t>
+          <t>papers/NLP/Embeddings/2017 Efficient Natural Language Response Suggestion_for Smart Reply.pdf</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5331,7 +5331,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2019 SBERT.pdf</t>
+          <t>papers/NLP/Embeddings/2019 SBERT.pdf</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5353,7 +5353,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2020 Realm_ Retrieval-_augmented language model pre-training.pdf</t>
+          <t>papers/NLP/Embeddings/2020 Realm_ Retrieval-_augmented language model pre-training.pdf</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5375,7 +5375,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2021 Augmented SBERT.pdf</t>
+          <t>papers/NLP/Embeddings/2021 Augmented SBERT.pdf</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5397,7 +5397,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2021 GTR.pdf</t>
+          <t>papers/NLP/Embeddings/2021 GTR.pdf</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5419,7 +5419,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2021 Scaling Deep Contrastive Learning Batch Size_under Memory Limited Setup.pdf</t>
+          <t>papers/NLP/Embeddings/2021 Scaling Deep Contrastive Learning Batch Size_under Memory Limited Setup.pdf</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5441,7 +5441,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2021 TSDAE_ Using Transformer-based Sequential Denoising Auto-Encoder_for Unsupervised Sentence Embedding Learning.pdf</t>
+          <t>papers/NLP/Embeddings/2021 TSDAE_ Using Transformer-based Sequential Denoising Auto-Encoder_for Unsupervised Sentence Embedding Learning.pdf</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5463,7 +5463,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2022 retroMAE v2.pdf</t>
+          <t>papers/NLP/Embeddings/2022 retroMAE v2.pdf</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5485,7 +5485,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2022 RetroMAE_.pdf</t>
+          <t>papers/NLP/Embeddings/2022 RetroMAE_.pdf</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5507,7 +5507,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2022 SimCSE.pdf</t>
+          <t>papers/NLP/Embeddings/2022 SimCSE.pdf</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2023 ANGLE-OPTIMIZED TEXT EMBEDDINGS.pdf</t>
+          <t>papers/NLP/Embeddings/2023 ANGLE-OPTIMIZED TEXT EMBEDDINGS.pdf</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2023 DEMYSTIFYING CLIP DATA.pdf</t>
+          <t>papers/NLP/Embeddings/2023 DEMYSTIFYING CLIP DATA.pdf</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5573,7 +5573,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2023 DiffCSE.pdf</t>
+          <t>papers/NLP/Embeddings/2023 DiffCSE.pdf</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5595,7 +5595,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2023 Improving Text Embeddings with_Large Language Models.pdf</t>
+          <t>papers/NLP/Embeddings/2023 Improving Text Embeddings with_Large Language Models.pdf</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5617,7 +5617,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/202312 Retro++.pdf</t>
+          <t>papers/NLP/Embeddings/202312 Retro++.pdf</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5639,7 +5639,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2024 Gecko.pdf</t>
+          <t>papers/NLP/Embeddings/2024 Gecko.pdf</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5661,7 +5661,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2024 LLM2Vec.pdf</t>
+          <t>papers/NLP/Embeddings/2024 LLM2Vec.pdf</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5683,7 +5683,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2024 Matryoshka Representation Learning.pdf</t>
+          <t>papers/NLP/Embeddings/2024 Matryoshka Representation Learning.pdf</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5705,7 +5705,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2024 Nomic Embed.pdf</t>
+          <t>papers/NLP/Embeddings/2024 Nomic Embed.pdf</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5727,7 +5727,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2024 Piccolo2.pdf</t>
+          <t>papers/NLP/Embeddings/2024 Piccolo2.pdf</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5749,7 +5749,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2024 Repetition Improves Language Model Embeddings.pdf</t>
+          <t>papers/NLP/Embeddings/2024 Repetition Improves Language Model Embeddings.pdf</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5771,7 +5771,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/2024 Scaling (Down) CLIP.pdf</t>
+          <t>papers/NLP/Embeddings/2024 Scaling (Down) CLIP.pdf</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5793,7 +5793,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/A Gradient Accumulation Method for Dense_Retriever under Memory Constraint.pdf</t>
+          <t>papers/NLP/Embeddings/A Gradient Accumulation Method for Dense_Retriever under Memory Constraint.pdf</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5815,7 +5815,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Embeddings/Improving Text Embeddings for Smaller Language Models.pdf</t>
+          <t>papers/NLP/Embeddings/Improving Text Embeddings for Smaller Language Models.pdf</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5837,7 +5837,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/2023 Distilling Step-by-Step.pdf</t>
+          <t>papers/NLP/Finetune/2023 Distilling Step-by-Step.pdf</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5859,7 +5859,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/2023 Less Is More for Alignment.pdf</t>
+          <t>papers/NLP/Finetune/2023 Less Is More for Alignment.pdf</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5881,7 +5881,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/2024 BLADE.pdf</t>
+          <t>papers/NLP/Finetune/2024 BLADE.pdf</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5903,7 +5903,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/2024 DINO Direct Nash Optimization.pdf</t>
+          <t>papers/NLP/Finetune/2024 DINO Direct Nash Optimization.pdf</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5925,7 +5925,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/2024 In-Context Learning Sufficient for Instruction Following in LLMs.pdf</t>
+          <t>papers/NLP/Finetune/2024 In-Context Learning Sufficient for Instruction Following in LLMs.pdf</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5947,7 +5947,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/2024 Instruction-tuned Language Models are Better Knowledge Learners.pdf</t>
+          <t>papers/NLP/Finetune/2024 Instruction-tuned Language Models are Better Knowledge Learners.pdf</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5969,7 +5969,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/2024 Self-Play Fine-Tuning.pdf</t>
+          <t>papers/NLP/Finetune/2024 Self-Play Fine-Tuning.pdf</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5991,7 +5991,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/2024 Toward Self-Improvement of LLMs via Imagination,_Searching, and Criticizing.pdf</t>
+          <t>papers/NLP/Finetune/2024 Toward Self-Improvement of LLMs via Imagination,_Searching, and Criticizing.pdf</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6013,7 +6013,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Knowledge/2020 Dense Passage Retrieval for Open-Domain Question Answering.pdf</t>
+          <t>papers/NLP/Knowledge/2020 Dense Passage Retrieval for Open-Domain Question Answering.pdf</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Knowledge/2021 ANSWERING COMPLEX OPEN-DOMAIN QUESTIONS_WITH MULTI-HOP DENSE RETRIEVAL.pdf</t>
+          <t>papers/NLP/Knowledge/2021 ANSWERING COMPLEX OPEN-DOMAIN QUESTIONS_WITH MULTI-HOP DENSE RETRIEVAL.pdf</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6057,7 +6057,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Knowledge/2023 ANSWERING COMPLEX OPEN-DOMAIN QUESTIONS_WITH MULTI-HOP DENSE RETRIEVAL.pdf</t>
+          <t>papers/NLP/Knowledge/2023 ANSWERING COMPLEX OPEN-DOMAIN QUESTIONS_WITH MULTI-HOP DENSE RETRIEVAL.pdf</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6079,7 +6079,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Knowledge/2023 Knowledge Graph Prompting for Multi-Document Question Answering.pdf</t>
+          <t>papers/NLP/Knowledge/2023 Knowledge Graph Prompting for Multi-Document Question Answering.pdf</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6101,7 +6101,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Knowledge/2024 KG roadmap.pdf</t>
+          <t>papers/NLP/Knowledge/2024 KG roadmap.pdf</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6123,7 +6123,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Knowledge/2024 RAG VS FINE-TUNING.pdf</t>
+          <t>papers/NLP/Knowledge/2024 RAG VS FINE-TUNING.pdf</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6145,7 +6145,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Knowledge/2024 Self-discovery.pdf</t>
+          <t>papers/NLP/Knowledge/2024 Self-discovery.pdf</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6167,7 +6167,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Knowledge/202408  A Graph RAG Approach to_Query-Focused Summarization.pdf</t>
+          <t>papers/NLP/Knowledge/202408  A Graph RAG Approach to_Query-Focused Summarization.pdf</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6189,7 +6189,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Knowledge/MUTUAL REASONING MAKES SMALLER LLMS_STRONGER PROBLEM-SOLVERS.pdf</t>
+          <t>papers/NLP/Knowledge/MUTUAL REASONING MAKES SMALLER LLMS_STRONGER PROBLEM-SOLVERS.pdf</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6211,7 +6211,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Learning/2022 Chinchilla.pdf</t>
+          <t>papers/NLP/Learning/2022 Chinchilla.pdf</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Learning/2022 Scaling Language Models_ Methods, Analysis_&amp; Insights from Training Gopher.pdf</t>
+          <t>papers/NLP/Learning/2022 Scaling Language Models_ Methods, Analysis_&amp; Insights from Training Gopher.pdf</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6255,7 +6255,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Learning/2023 Small-scale proxies for large-scale Transformer training instabilities.pdf</t>
+          <t>papers/NLP/Learning/2023 Small-scale proxies for large-scale Transformer training instabilities.pdf</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6277,7 +6277,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Learning/2024 Stealing Part of a Production Language Model.pdf</t>
+          <t>papers/NLP/Learning/2024 Stealing Part of a Production Language Model.pdf</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6299,7 +6299,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Learning/2024 Towards Optimal Learning of Language Models.pdf</t>
+          <t>papers/NLP/Learning/2024 Towards Optimal Learning of Language Models.pdf</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6321,7 +6321,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Learning/language_models_are_unsupervised_multitask_learners.pdf</t>
+          <t>papers/NLP/Learning/language_models_are_unsupervised_multitask_learners.pdf</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6339,7 +6339,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Learning/Professor Forcing.pdf</t>
+          <t>papers/NLP/Learning/Professor Forcing.pdf</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6361,7 +6361,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Learning/Teaching Small Language Models to Reason.pdf</t>
+          <t>papers/NLP/Learning/Teaching Small Language Models to Reason.pdf</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6383,7 +6383,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LLM Agent/2024 LLM Agent Operating System.pdf</t>
+          <t>papers/NLP/LLM Agent/2024 LLM Agent Operating System.pdf</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6405,7 +6405,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LLM Agent/pearl.pdf</t>
+          <t>papers/NLP/LLM Agent/pearl.pdf</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6427,7 +6427,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2019 Sparse Transformer.pdf</t>
+          <t>papers/NLP/LongContext/2019 Sparse Transformer.pdf</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6449,7 +6449,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2022 LongT5.pdf</t>
+          <t>papers/NLP/LongContext/2022 LongT5.pdf</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6471,7 +6471,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2023 Cache Transformers.pdf</t>
+          <t>papers/NLP/LongContext/2023 Cache Transformers.pdf</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6493,7 +6493,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2023 COLT5.pdf</t>
+          <t>papers/NLP/LongContext/2023 COLT5.pdf</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6515,7 +6515,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2023 Focused Transformer.pdf</t>
+          <t>papers/NLP/LongContext/2023 Focused Transformer.pdf</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6537,7 +6537,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2023 SLED (long document).pdf</t>
+          <t>papers/NLP/LongContext/2023 SLED (long document).pdf</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6555,7 +6555,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2024 Data Engineering for Scaling Language Models to 128K Context.pdf</t>
+          <t>papers/NLP/LongContext/2024 Data Engineering for Scaling Language Models to 128K Context.pdf</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6577,7 +6577,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2024 In Search of Needles in a 10M Haystack(1).pdf</t>
+          <t>papers/NLP/LongContext/2024 In Search of Needles in a 10M Haystack(1).pdf</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -6599,7 +6599,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2024 In Search of Needles in a 10M Haystack.pdf</t>
+          <t>papers/NLP/LongContext/2024 In Search of Needles in a 10M Haystack.pdf</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -6621,7 +6621,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2024 In Search of Needles in a 11M Haystack.pdf</t>
+          <t>papers/NLP/LongContext/2024 In Search of Needles in a 11M Haystack.pdf</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6643,7 +6643,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2024 Infinite Context Transformers .pdf</t>
+          <t>papers/NLP/LongContext/2024 Infinite Context Transformers .pdf</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6665,7 +6665,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2024 LLM Maybe LongLM.pdf</t>
+          <t>papers/NLP/LongContext/2024 LLM Maybe LongLM.pdf</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6687,7 +6687,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2024 LongAlign.pdf</t>
+          <t>papers/NLP/LongContext/2024 LongAlign.pdf</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6709,7 +6709,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2024 TransformerFAM.pdf</t>
+          <t>papers/NLP/LongContext/2024 TransformerFAM.pdf</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6731,7 +6731,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/2024 Transformers Can Achieve Length_Generalization But Not Robustly.pdf</t>
+          <t>papers/NLP/LongContext/2024 Transformers Can Achieve Length_Generalization But Not Robustly.pdf</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6753,7 +6753,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/202407 Summary of a Haystack.pdf</t>
+          <t>papers/NLP/LongContext/202407 Summary of a Haystack.pdf</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -6775,7 +6775,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/202408 Dolphin.pdf</t>
+          <t>papers/NLP/LongContext/202408 Dolphin.pdf</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6797,7 +6797,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/An Exploration of Hierarchical Attention Transformers_for Efficient Long Document Classification.pdf</t>
+          <t>papers/NLP/LongContext/An Exploration of Hierarchical Attention Transformers_for Efficient Long Document Classification.pdf</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/CLASSIFICATION OF LONG SEQUENTIAL DATA USING_CIRCULAR DILATED CONVOLUTIONAL NEURAL NETWORKS.pdf</t>
+          <t>papers/NLP/LongContext/CLASSIFICATION OF LONG SEQUENTIAL DATA USING_CIRCULAR DILATED CONVOLUTIONAL NEURAL NETWORKS.pdf</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -6841,7 +6841,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Efficient Classification of Long Documents Using Transformers.pdf</t>
+          <t>papers/NLP/LongContext/Efficient Classification of Long Documents Using Transformers.pdf</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -6859,7 +6859,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/HIERARCHICAL TRANSFORMERS FOR LONG DOCUMENT CLASSIFICATION.pdf</t>
+          <t>papers/NLP/LongContext/HIERARCHICAL TRANSFORMERS FOR LONG DOCUMENT CLASSIFICATION.pdf</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -6881,7 +6881,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Revisiting Transformer-based Models for Long Document Classification.pdf</t>
+          <t>papers/NLP/LongContext/Revisiting Transformer-based Models for Long Document Classification.pdf</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -6899,7 +6899,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2019 BART.pdf</t>
+          <t>papers/NLP/Models/2019 BART.pdf</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -6921,7 +6921,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2022 InstructGPT.pdf</t>
+          <t>papers/NLP/Models/2022 InstructGPT.pdf</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -6943,7 +6943,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2022 PalM.pdf</t>
+          <t>papers/NLP/Models/2022 PalM.pdf</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -6965,7 +6965,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2023 Code LLaMa.pdf</t>
+          <t>papers/NLP/Models/2023 Code LLaMa.pdf</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -6987,7 +6987,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2023 deBERTinha.pdf</t>
+          <t>papers/NLP/Models/2023 deBERTinha.pdf</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -7009,7 +7009,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2023 Gemini.pdf</t>
+          <t>papers/NLP/Models/2023 Gemini.pdf</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -7027,7 +7027,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2023 LLAMA 2.pdf</t>
+          <t>papers/NLP/Models/2023 LLAMA 2.pdf</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -7045,7 +7045,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2023 Mistral 7B.pdf</t>
+          <t>papers/NLP/Models/2023 Mistral 7B.pdf</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -7067,7 +7067,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2023 Orca 2.pdf</t>
+          <t>papers/NLP/Models/2023 Orca 2.pdf</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -7089,7 +7089,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2023 Orca.pdf</t>
+          <t>papers/NLP/Models/2023 Orca.pdf</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -7111,7 +7111,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2023 Phi 1-5.pdf</t>
+          <t>papers/NLP/Models/2023 Phi 1-5.pdf</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -7133,7 +7133,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2023 PHI 1.pdf</t>
+          <t>papers/NLP/Models/2023 PHI 1.pdf</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -7155,7 +7155,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2023 Phi.pdf</t>
+          <t>papers/NLP/Models/2023 Phi.pdf</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -7177,7 +7177,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2023 Solar 10.7B.pdf</t>
+          <t>papers/NLP/Models/2023 Solar 10.7B.pdf</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -7199,7 +7199,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2023 ZEPHYR_ DIRECT DISTILLATION OF LM ALIGNMENT.pdf</t>
+          <t>papers/NLP/Models/2023 ZEPHYR_ DIRECT DISTILLATION OF LM ALIGNMENT.pdf</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -7221,7 +7221,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2024 DeepSeek-V2.pdf</t>
+          <t>papers/NLP/Models/2024 DeepSeek-V2.pdf</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -7243,7 +7243,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2024 Gemini 1_5.pdf</t>
+          <t>papers/NLP/Models/2024 Gemini 1_5.pdf</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -7261,7 +7261,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2024 gemini_v1_5_report.pdf</t>
+          <t>papers/NLP/Models/2024 gemini_v1_5_report.pdf</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -7279,7 +7279,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2024 gemma-report.pdf</t>
+          <t>papers/NLP/Models/2024 gemma-report.pdf</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -7297,7 +7297,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2024 Olmo.pdf</t>
+          <t>papers/NLP/Models/2024 Olmo.pdf</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -7319,7 +7319,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2024 Phi-3.pdf</t>
+          <t>papers/NLP/Models/2024 Phi-3.pdf</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -7341,7 +7341,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/2024 Yi.pdf</t>
+          <t>papers/NLP/Models/2024 Yi.pdf</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -7363,7 +7363,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/202407 LLAMA 3.1.pdf</t>
+          <t>papers/NLP/Models/202407 LLAMA 3.1.pdf</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -7381,7 +7381,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/20240731 GEMMA 2.pdf</t>
+          <t>papers/NLP/Models/20240731 GEMMA 2.pdf</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -7403,7 +7403,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/202408 EXAONE 3.0 7.8B .pdf</t>
+          <t>papers/NLP/Models/202408 EXAONE 3.0 7.8B .pdf</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -7425,7 +7425,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/BERT.pdf</t>
+          <t>papers/NLP/Models/BERT.pdf</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -7447,7 +7447,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/gemma-2-report.pdf</t>
+          <t>papers/NLP/Models/gemma-2-report.pdf</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -7465,7 +7465,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/GPT.pdf</t>
+          <t>papers/NLP/Models/GPT.pdf</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -7483,7 +7483,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/GPT2.pdf</t>
+          <t>papers/NLP/Models/GPT2.pdf</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -7501,7 +7501,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/GPT3.pdf</t>
+          <t>papers/NLP/Models/GPT3.pdf</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -7523,7 +7523,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/LLamA.pdf</t>
+          <t>papers/NLP/Models/LLamA.pdf</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -7541,7 +7541,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/roBERTa(1).pdf</t>
+          <t>papers/NLP/Models/roBERTa(1).pdf</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -7563,7 +7563,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/RoBERTa.pdf</t>
+          <t>papers/NLP/Models/RoBERTa.pdf</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -7585,7 +7585,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/Sabia.pdf</t>
+          <t>papers/NLP/Models/Sabia.pdf</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -7607,7 +7607,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/T5.pdf</t>
+          <t>papers/NLP/Models/T5.pdf</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -7629,7 +7629,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/MoE/2023 Mixture-of-Experts Meets Instruction Tuning.pdf</t>
+          <t>papers/NLP/MoE/2023 Mixture-of-Experts Meets Instruction Tuning.pdf</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -7651,7 +7651,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/MoE/2023 Towards MoE Deployment_ Mitigating Inefficiencies_in Mixture-of-Expert (MoE) Inference.pdf</t>
+          <t>papers/NLP/MoE/2023 Towards MoE Deployment_ Mitigating Inefficiencies_in Mixture-of-Expert (MoE) Inference.pdf</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -7673,7 +7673,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/MoE/2024 Camelidae-8x34B.pdf</t>
+          <t>papers/NLP/MoE/2024 Camelidae-8x34B.pdf</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -7695,7 +7695,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/MoE/2024 DeepSeekMoE.pdf</t>
+          <t>papers/NLP/MoE/2024 DeepSeekMoE.pdf</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -7717,7 +7717,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/MoE/2024 Mixing Expert LLMs into a Mixture-of-Experts LLM.pdf</t>
+          <t>papers/NLP/MoE/2024 Mixing Expert LLMs into a Mixture-of-Experts LLM.pdf</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -7739,7 +7739,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/MoE/2024 Mixtral.pdf</t>
+          <t>papers/NLP/MoE/2024 Mixtral.pdf</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -7761,7 +7761,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/MoE/2024 Mixture-of-Depths.pdf</t>
+          <t>papers/NLP/MoE/2024 Mixture-of-Depths.pdf</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -7783,7 +7783,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/MoE/2024 Yuan 2.0-M32.pdf</t>
+          <t>papers/NLP/MoE/2024 Yuan 2.0-M32.pdf</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -7801,7 +7801,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/MoE/202407 Mixture of A Million Experts.pdf</t>
+          <t>papers/NLP/MoE/202407 Mixture of A Million Experts.pdf</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -7823,7 +7823,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/MoE/202409 GRIN_ GRadient-INformed MoE.pdf</t>
+          <t>papers/NLP/MoE/202409 GRIN_ GRadient-INformed MoE.pdf</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -7845,7 +7845,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/OCR/2023 UDOP.pdf</t>
+          <t>papers/NLP/OCR/2023 UDOP.pdf</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -7867,7 +7867,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/OCR/202409 Towards OCR-2.0_via a Unified End-to-end Model.pdf</t>
+          <t>papers/NLP/OCR/202409 Towards OCR-2.0_via a Unified End-to-end Model.pdf</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -7889,7 +7889,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Portuguese/2020 BertimBau.pdf</t>
+          <t>papers/NLP/Portuguese/2020 BertimBau.pdf</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -7907,7 +7907,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Portuguese/2020 PTT5.pdf</t>
+          <t>papers/NLP/Portuguese/2020 PTT5.pdf</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -7929,7 +7929,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Portuguese/2022 Portuguese_SQuAD v1.1.pdf</t>
+          <t>papers/NLP/Portuguese/2022 Portuguese_SQuAD v1.1.pdf</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -7947,7 +7947,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/PositionalEncoding/2020 Improve Transformer Models with Better Relative Position Embeddings.pdf</t>
+          <t>papers/NLP/PositionalEncoding/2020 Improve Transformer Models with Better Relative Position Embeddings.pdf</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -7969,7 +7969,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/PositionalEncoding/2022 ALiBi.pdf</t>
+          <t>papers/NLP/PositionalEncoding/2022 ALiBi.pdf</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -7991,7 +7991,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/PositionalEncoding/2024 LASER.pdf</t>
+          <t>papers/NLP/PositionalEncoding/2024 LASER.pdf</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -8013,7 +8013,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/PositionalEncoding/2024 LongRope.pdf</t>
+          <t>papers/NLP/PositionalEncoding/2024 LongRope.pdf</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -8035,7 +8035,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/PositionalEncoding/2024 Resonance RoPE.pdf</t>
+          <t>papers/NLP/PositionalEncoding/2024 Resonance RoPE.pdf</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -8057,7 +8057,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/PositionalEncoding/Improve Transformer Models with Better Relative Position Embeddings.pdf</t>
+          <t>papers/NLP/PositionalEncoding/Improve Transformer Models with Better Relative Position Embeddings.pdf</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -8079,7 +8079,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/PositionalEncoding/Roformer_ En-_hanced transformer with rotary position embedding.pdf</t>
+          <t>papers/NLP/PositionalEncoding/Roformer_ En-_hanced transformer with rotary position embedding.pdf</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/PositionalEncoding/Self-Attention with Relative Position Representations.pdf</t>
+          <t>papers/NLP/PositionalEncoding/Self-Attention with Relative Position Representations.pdf</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -8123,7 +8123,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Pruning/2024 Ineffectiveness of the Deeper Layers.pdf</t>
+          <t>papers/NLP/Pruning/2024 Ineffectiveness of the Deeper Layers.pdf</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -8145,7 +8145,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Pruning/202408 Compact Language Models via Pruning and_Knowledge Distillation.pdf</t>
+          <t>papers/NLP/Pruning/202408 Compact Language Models via Pruning and_Knowledge Distillation.pdf</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -8167,7 +8167,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Quantization/2024 Memory-Efficient LLM Training by Gradient Low-Rank Projection.pdf</t>
+          <t>papers/NLP/Quantization/2024 Memory-Efficient LLM Training by Gradient Low-Rank Projection.pdf</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -8189,7 +8189,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Quantization/2024 The era of 1 bit LLMs.pdf</t>
+          <t>papers/NLP/Quantization/2024 The era of 1 bit LLMs.pdf</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -8211,7 +8211,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/RAG/2024 MultiHop-RAG.pdf</t>
+          <t>papers/NLP/RAG/2024 MultiHop-RAG.pdf</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -8233,7 +8233,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/RAG/2024 RAFT.pdf</t>
+          <t>papers/NLP/RAG/2024 RAFT.pdf</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -8255,7 +8255,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/RAG/202407 RankRAG.pdf</t>
+          <t>papers/NLP/RAG/202407 RankRAG.pdf</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -8277,7 +8277,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/RAG/202408 Improving Retrieval Augmented Language Model with Self-Reasoning.pdf</t>
+          <t>papers/NLP/RAG/202408 Improving Retrieval Augmented Language Model with Self-Reasoning.pdf</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -8299,7 +8299,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/RAG/2025 RAG survey.pdf</t>
+          <t>papers/NLP/RAG/2025 RAG survey.pdf</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -8321,7 +8321,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/RAG/Searching for Best Practices in Retrieval-Augmented_Generation.pdf</t>
+          <t>papers/NLP/RAG/Searching for Best Practices in Retrieval-Augmented_Generation.pdf</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -8343,7 +8343,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/RNNs/202407 Learning to (Learn at Test Time).pdf</t>
+          <t>papers/NLP/RNNs/202407 Learning to (Learn at Test Time).pdf</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -8365,7 +8365,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/State spaces/2024 DenseMamba.pdf</t>
+          <t>papers/NLP/State spaces/2024 DenseMamba.pdf</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -8387,7 +8387,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/State spaces/2024 Jamba.pdf</t>
+          <t>papers/NLP/State spaces/2024 Jamba.pdf</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -8409,7 +8409,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/State spaces/2024 MambaFormer.pdf</t>
+          <t>papers/NLP/State spaces/2024 MambaFormer.pdf</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -8431,7 +8431,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/State spaces/2024 Transformers are better than ssms on copying.pdf</t>
+          <t>papers/NLP/State spaces/2024 Transformers are better than ssms on copying.pdf</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/State spaces/202405 Mamba.pdf</t>
+          <t>papers/NLP/State spaces/202405 Mamba.pdf</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -8475,7 +8475,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/State spaces/202407 Mamba 2.pdf</t>
+          <t>papers/NLP/State spaces/202407 Mamba 2.pdf</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -8497,7 +8497,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/State spaces/202407 Samba.pdf</t>
+          <t>papers/NLP/State spaces/202407 Samba.pdf</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -8519,7 +8519,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Summarization/2019 Pegasus.pdf</t>
+          <t>papers/NLP/Summarization/2019 Pegasus.pdf</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -8541,7 +8541,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Tokenization/2015 BPE.pdf</t>
+          <t>papers/NLP/Tokenization/2015 BPE.pdf</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -8563,7 +8563,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Tokenization/2018 SentencePiece.pdf</t>
+          <t>papers/NLP/Tokenization/2018 SentencePiece.pdf</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -8585,7 +8585,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Training/202408 Exploring Impact of Code in Pre-training.pdf</t>
+          <t>papers/NLP/Training/202408 Exploring Impact of Code in Pre-training.pdf</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -8607,7 +8607,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Training/Efficient Training of Language Models to_Fill in the Middle.pdf</t>
+          <t>papers/NLP/Training/Efficient Training of Language Models to_Fill in the Middle.pdf</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -8629,7 +8629,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Video/Consistency/202407 FreeLong.pdf</t>
+          <t>papers/Video/Consistency/202407 FreeLong.pdf</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -8651,7 +8651,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Image/Autoencoder/Quantized/Hierarchical Residual Learning Based Vector_Quantized Variational Autoencoder for_Image Reconstruction and Generation.pdf</t>
+          <t>papers/Image/Autoencoder/Quantized/Hierarchical Residual Learning Based Vector_Quantized Variational Autoencoder for_Image Reconstruction and Generation.pdf</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -8673,7 +8673,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Image/Segmentation/Models/202408 Segment Anything 2.pdf</t>
+          <t>papers/Image/Segmentation/Models/202408 Segment Anything 2.pdf</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -8695,7 +8695,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/Image/Segmentation/Models/Segment Anything.pdf</t>
+          <t>papers/Image/Segmentation/Models/Segment Anything.pdf</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -8713,7 +8713,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Agents/Memory/2023 WALKING DOWN THE MEMORY MAZE.pdf</t>
+          <t>papers/NLP/Agents/Memory/2023 WALKING DOWN THE MEMORY MAZE.pdf</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -8735,7 +8735,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Datasets/Syntetic/2024 Best Practices and Lessons Learned on_Synthetic Data.pdf</t>
+          <t>papers/NLP/Datasets/Syntetic/2024 Best Practices and Lessons Learned on_Synthetic Data.pdf</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -8757,7 +8757,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Datasets/Syntetic/20240614 Alignment Data Synthesis from Scratch.pdf</t>
+          <t>papers/NLP/Datasets/Syntetic/20240614 Alignment Data Synthesis from Scratch.pdf</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -8779,7 +8779,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Dataset/2023 FLAN.pdf</t>
+          <t>papers/NLP/Finetune/Dataset/2023 FLAN.pdf</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -8801,7 +8801,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Dataset/2024 RewardBench.pdf</t>
+          <t>papers/NLP/Finetune/Dataset/2024 RewardBench.pdf</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -8823,7 +8823,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Efficient/2019 Adapter.pdf</t>
+          <t>papers/NLP/Finetune/Efficient/2019 Adapter.pdf</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -8845,7 +8845,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Efficient/2021 Lora.pdf</t>
+          <t>papers/NLP/Finetune/Efficient/2021 Lora.pdf</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -8867,7 +8867,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Efficient/2023 LLama adapter.pdf</t>
+          <t>papers/NLP/Finetune/Efficient/2023 LLama adapter.pdf</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -8889,7 +8889,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Efficient/2023 qLoRa.pdf</t>
+          <t>papers/NLP/Finetune/Efficient/2023 qLoRa.pdf</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -8911,7 +8911,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Efficient/2024 DORA.pdf</t>
+          <t>papers/NLP/Finetune/Efficient/2024 DORA.pdf</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -8933,7 +8933,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Efficient/2024 LoRA Learns Less and Forgets Less.pdf</t>
+          <t>papers/NLP/Finetune/Efficient/2024 LoRA Learns Less and Forgets Less.pdf</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -8955,7 +8955,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Preference/2023 Direct Preference Optimization(1).pdf</t>
+          <t>papers/NLP/Finetune/Preference/2023 Direct Preference Optimization(1).pdf</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -8977,7 +8977,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Preference/2023 Direct Preference Optimization.pdf</t>
+          <t>papers/NLP/Finetune/Preference/2023 Direct Preference Optimization.pdf</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -8999,7 +8999,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Preference/2024 ORPO.pdf</t>
+          <t>papers/NLP/Finetune/Preference/2024 ORPO.pdf</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -9021,7 +9021,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Preference/2024 sDPO.pdf</t>
+          <t>papers/NLP/Finetune/Preference/2024 sDPO.pdf</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Preference/2024 SimPO.pdf</t>
+          <t>papers/NLP/Finetune/Preference/2024 SimPO.pdf</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -9065,7 +9065,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Reinforcement/2023 Reinforced Self-Training (ReST) for Language_Modeling.pdf</t>
+          <t>papers/NLP/Finetune/Reinforcement/2023 Reinforced Self-Training (ReST) for Language_Modeling.pdf</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -9087,7 +9087,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Reinforcement/2023 RLAIF_ Scaling Reinforcement Learning from Human Feedback with AI_Feedback.pdf</t>
+          <t>papers/NLP/Finetune/Reinforcement/2023 RLAIF_ Scaling Reinforcement Learning from Human Feedback with AI_Feedback.pdf</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -9109,7 +9109,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Reinforcement/2024 Teaching Large Language Models to Reason_with Reinforcement Learning.pdf</t>
+          <t>papers/NLP/Finetune/Reinforcement/2024 Teaching Large Language Models to Reason_with Reinforcement Learning.pdf</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -9131,7 +9131,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Reinforcement/20240612 REINFORCE Style_Optimization.pdf</t>
+          <t>papers/NLP/Finetune/Reinforcement/20240612 REINFORCE Style_Optimization.pdf</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -9153,7 +9153,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Reinforcement/202407 A General_Framework for Steerable Multi-Objective_Finetuning.pdf</t>
+          <t>papers/NLP/Finetune/Reinforcement/202407 A General_Framework for Steerable Multi-Objective_Finetuning.pdf</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -9175,7 +9175,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Reinforcement/202407 The Importance of Online Data.pdf</t>
+          <t>papers/NLP/Finetune/Reinforcement/202407 The Importance of Online Data.pdf</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -9197,7 +9197,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Reinforcement/20240723 J-BOND.pdf</t>
+          <t>papers/NLP/Finetune/Reinforcement/20240723 J-BOND.pdf</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -9219,7 +9219,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Reinforcement/Deep Reinforcement Learning_from Human Preferences.pdf</t>
+          <t>papers/NLP/Finetune/Reinforcement/Deep Reinforcement Learning_from Human Preferences.pdf</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -9241,7 +9241,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Reinforcement/Training language models to follow instructions with human feedback.pdf</t>
+          <t>papers/NLP/Finetune/Reinforcement/Training language models to follow instructions with human feedback.pdf</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -9263,7 +9263,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Attention/2023 LM Infinite.pdf</t>
+          <t>papers/NLP/LongContext/Attention/2023 LM Infinite.pdf</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -9285,7 +9285,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Attention/2023 LongNet.pdf</t>
+          <t>papers/NLP/LongContext/Attention/2023 LongNet.pdf</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -9307,7 +9307,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Attention/Longformer.pdf</t>
+          <t>papers/NLP/LongContext/Attention/Longformer.pdf</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -9329,7 +9329,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Memory/2022 MEMORIZING TRANSFORMERS.pdf</t>
+          <t>papers/NLP/LongContext/Memory/2022 MEMORIZING TRANSFORMERS.pdf</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -9351,7 +9351,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Memory/2022 Recurrent Memory Transformer.pdf</t>
+          <t>papers/NLP/LongContext/Memory/2022 Recurrent Memory Transformer.pdf</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -9373,7 +9373,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Memory/202406 Extended Mind Transformers.pdf</t>
+          <t>papers/NLP/LongContext/Memory/202406 Extended Mind Transformers.pdf</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -9395,7 +9395,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Memory/202407 Associative Recurrent Memory Transformer.pdf</t>
+          <t>papers/NLP/LongContext/Memory/202407 Associative Recurrent Memory Transformer.pdf</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -9417,7 +9417,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Memory/Associative Recurrent Memory Transformer.pdf</t>
+          <t>papers/NLP/LongContext/Memory/Associative Recurrent Memory Transformer.pdf</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -9439,7 +9439,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Memory/HUMAN-LIKE EPISODIC MEMORY FOR INFINITE CONTEXT LLMS.pdf</t>
+          <t>papers/NLP/LongContext/Memory/HUMAN-LIKE EPISODIC MEMORY FOR INFINITE CONTEXT LLMS.pdf</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -9461,7 +9461,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Positional encoding/2022  A length-extrapolatable transformer.pdf</t>
+          <t>papers/NLP/LongContext/Positional encoding/2022  A length-extrapolatable transformer.pdf</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -9483,7 +9483,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Positional encoding/2023 Effective Long-Context Scaling of Foundation Models(1).pdf</t>
+          <t>papers/NLP/LongContext/Positional encoding/2023 Effective Long-Context Scaling of Foundation Models(1).pdf</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -9501,7 +9501,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Positional encoding/2023 Effective Long-Context Scaling of Foundation Models.pdf</t>
+          <t>papers/NLP/LongContext/Positional encoding/2023 Effective Long-Context Scaling of Foundation Models.pdf</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -9523,7 +9523,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Positional encoding/2023 EXTENDING CONTEXT WINDOW OF LARGE LAN-_GUAGE MODELS VIA POSITION INTERPOLATION.pdf</t>
+          <t>papers/NLP/LongContext/Positional encoding/2023 EXTENDING CONTEXT WINDOW OF LARGE LAN-_GUAGE MODELS VIA POSITION INTERPOLATION.pdf</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -9545,7 +9545,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Positional encoding/2023 EXTENDING CONTEXT WINDOW OF LARGE.pdf</t>
+          <t>papers/NLP/LongContext/Positional encoding/2023 EXTENDING CONTEXT WINDOW OF LARGE.pdf</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -9567,7 +9567,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Positional encoding/2023 Functional Interpolation for Relative Positions.pdf</t>
+          <t>papers/NLP/LongContext/Positional encoding/2023 Functional Interpolation for Relative Positions.pdf</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -9589,7 +9589,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Positional encoding/2023 The Impact of Positional Encoding on Length Generalizartion.pdf</t>
+          <t>papers/NLP/LongContext/Positional encoding/2023 The Impact of Positional Encoding on Length Generalizartion.pdf</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -9611,7 +9611,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Positional encoding/2023 YaRN_ Efficient Context Window Extension of Large_Language Models.pdf</t>
+          <t>papers/NLP/LongContext/Positional encoding/2023 YaRN_ Efficient Context Window Extension of Large_Language Models.pdf</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -9629,7 +9629,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Positional encoding/2024 POSE.pdf</t>
+          <t>papers/NLP/LongContext/Positional encoding/2024 POSE.pdf</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -9651,7 +9651,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/LongContext/Positional encoding/2024 Transformers Can Achieve Length_Generalization But Not Robustly.pdf</t>
+          <t>papers/NLP/LongContext/Positional encoding/2024 Transformers Can Achieve Length_Generalization But Not Robustly.pdf</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -9673,7 +9673,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/Small/2024 BioMedLM.pdf</t>
+          <t>papers/NLP/Models/Small/2024 BioMedLM.pdf</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -9695,7 +9695,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/Small/2024 MobiLLama.pdf</t>
+          <t>papers/NLP/Models/Small/2024 MobiLLama.pdf</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -9717,7 +9717,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Models/Small/202407 MobileLLM.pdf</t>
+          <t>papers/NLP/Models/Small/202407 MobileLLM.pdf</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -9739,7 +9739,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Reasoning/Finetune/2024 Quiet-STaR.pdf</t>
+          <t>papers/NLP/Reasoning/Finetune/2024 Quiet-STaR.pdf</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -9761,7 +9761,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Reasoning/Finetune/202409 Quiet-STaR.pdf</t>
+          <t>papers/NLP/Reasoning/Finetune/202409 Quiet-STaR.pdf</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -9783,7 +9783,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Reasoning/Finetune/202409 Training Language Models_with Reflection for Mathematical Reasoning.pdf</t>
+          <t>papers/NLP/Reasoning/Finetune/202409 Training Language Models_with Reflection for Mathematical Reasoning.pdf</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -9805,7 +9805,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Sampling/Search/Scaling LLM Test-Time Compute Optimally can_be More Effective.pdf</t>
+          <t>papers/NLP/Sampling/Search/Scaling LLM Test-Time Compute Optimally can_be More Effective.pdf</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -9827,7 +9827,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>C:/Users/Luis Felipe Chary/Downloads/papers/Papers/NLP/Finetune/Dataset/Generation/2024 GLAM.pdf</t>
+          <t>papers/NLP/Finetune/Dataset/Generation/2024 GLAM.pdf</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
